--- a/product-definitions/spreadsheet/depolarisation-ratio.xlsx
+++ b/product-definitions/spreadsheet/depolarisation-ratio.xlsx
@@ -375,7 +375,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -395,11 +395,6 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -436,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -458,14 +453,11 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -474,32 +466,32 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="5" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -508,17 +500,14 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="11" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,7 +858,7 @@
       <c r="A4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C4" s="6" t="s">
@@ -914,7 +903,7 @@
         <v>15000.0</v>
       </c>
       <c r="D5" s="4"/>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4"/>
@@ -950,7 +939,7 @@
         <v>2.0</v>
       </c>
       <c r="D6" s="4"/>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="4"/>
@@ -1210,7 +1199,7 @@
         <v>64.0</v>
       </c>
       <c r="D13" s="4"/>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="4"/>
@@ -1282,7 +1271,7 @@
         <v>1024.0</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="4"/>
@@ -7854,13 +7843,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>50</v>
       </c>
     </row>
@@ -7868,10 +7857,10 @@
       <c r="A2" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C2" s="10">
+      <c r="C2" s="9">
         <v>1.0</v>
       </c>
     </row>
@@ -7879,10 +7868,10 @@
       <c r="A3" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <v>1.0</v>
       </c>
     </row>
@@ -8903,22 +8892,22 @@
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>60</v>
       </c>
     </row>
@@ -8935,7 +8924,7 @@
       <c r="B3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D3" s="4"/>
@@ -8945,11 +8934,11 @@
       <c r="B4" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>65</v>
       </c>
       <c r="D4" s="4"/>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -8978,7 +8967,7 @@
       <c r="B7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>70</v>
       </c>
       <c r="D7" s="4"/>
@@ -8988,7 +8977,7 @@
       <c r="B8" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="15">
         <v>-1.0E20</v>
       </c>
       <c r="D8" s="4"/>
@@ -8998,7 +8987,7 @@
       <c r="B9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D9" s="4"/>
@@ -9008,29 +8997,29 @@
       <c r="B10" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D10" s="4"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="17"/>
+      <c r="A11" s="16"/>
       <c r="B11" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="16"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
       <c r="D12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="18" t="s">
         <v>77</v>
       </c>
       <c r="B13" s="4"/>
@@ -9042,7 +9031,7 @@
       <c r="B14" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D14" s="4"/>
@@ -9052,11 +9041,11 @@
       <c r="B15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>78</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -9065,7 +9054,7 @@
       <c r="B16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>80</v>
       </c>
       <c r="D16" s="4"/>
@@ -9075,8 +9064,8 @@
       <c r="B17" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="18" t="s">
         <v>77</v>
       </c>
     </row>
@@ -9085,7 +9074,7 @@
       <c r="B18" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="13" t="s">
         <v>81</v>
       </c>
       <c r="D18" s="4"/>
@@ -9095,7 +9084,7 @@
       <c r="B19" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="20">
+      <c r="C19" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D19" s="4"/>
@@ -9105,7 +9094,7 @@
       <c r="B20" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D20" s="4"/>
@@ -9115,7 +9104,7 @@
       <c r="B21" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D21" s="4"/>
@@ -9125,7 +9114,7 @@
       <c r="B22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D22" s="4"/>
@@ -9133,11 +9122,11 @@
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
-      <c r="C23" s="18"/>
+      <c r="C23" s="17"/>
       <c r="D23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="18" t="s">
         <v>82</v>
       </c>
       <c r="B24" s="4"/>
@@ -9149,7 +9138,7 @@
       <c r="B25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D25" s="4"/>
@@ -9159,11 +9148,11 @@
       <c r="B26" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>78</v>
       </c>
       <c r="D26" s="4"/>
-      <c r="F26" s="8" t="s">
+      <c r="F26" s="7" t="s">
         <v>79</v>
       </c>
     </row>
@@ -9172,7 +9161,7 @@
       <c r="B27" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="17" t="s">
         <v>80</v>
       </c>
       <c r="D27" s="4"/>
@@ -9182,8 +9171,8 @@
       <c r="B28" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19" t="s">
+      <c r="C28" s="17"/>
+      <c r="D28" s="18" t="s">
         <v>82</v>
       </c>
     </row>
@@ -9192,7 +9181,7 @@
       <c r="B29" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>83</v>
       </c>
       <c r="D29" s="4"/>
@@ -9202,7 +9191,7 @@
       <c r="B30" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="20">
+      <c r="C30" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D30" s="4"/>
@@ -9212,7 +9201,7 @@
       <c r="B31" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D31" s="4"/>
@@ -9222,7 +9211,7 @@
       <c r="B32" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D32" s="4"/>
@@ -9232,7 +9221,7 @@
       <c r="B33" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D33" s="4"/>
@@ -9240,11 +9229,11 @@
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="18"/>
+      <c r="C34" s="17"/>
       <c r="D34" s="4"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="19" t="s">
+      <c r="A35" s="18" t="s">
         <v>84</v>
       </c>
       <c r="B35" s="4"/>
@@ -9278,7 +9267,7 @@
       <c r="B36" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D36" s="4"/>
@@ -9310,12 +9299,12 @@
       <c r="B37" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>78</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="19"/>
+      <c r="F37" s="18"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -9342,7 +9331,7 @@
       <c r="B38" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>80</v>
       </c>
       <c r="D38" s="4"/>
@@ -9374,8 +9363,8 @@
       <c r="B39" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C39" s="18"/>
-      <c r="D39" s="19" t="s">
+      <c r="C39" s="17"/>
+      <c r="D39" s="18" t="s">
         <v>84</v>
       </c>
       <c r="E39" s="4"/>
@@ -9406,7 +9395,7 @@
       <c r="B40" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C40" s="14" t="s">
+      <c r="C40" s="13" t="s">
         <v>85</v>
       </c>
       <c r="D40" s="4"/>
@@ -9438,7 +9427,7 @@
       <c r="B41" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C41" s="20">
+      <c r="C41" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D41" s="4"/>
@@ -9470,7 +9459,7 @@
       <c r="B42" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="4"/>
@@ -9502,7 +9491,7 @@
       <c r="B43" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D43" s="4"/>
@@ -9534,7 +9523,7 @@
       <c r="B44" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D44" s="4"/>
@@ -9564,7 +9553,7 @@
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
-      <c r="C45" s="18"/>
+      <c r="C45" s="17"/>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -9590,7 +9579,7 @@
       <c r="Z45" s="4"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="18" t="s">
         <v>86</v>
       </c>
       <c r="B46" s="4"/>
@@ -9624,7 +9613,7 @@
       <c r="B47" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D47" s="4"/>
@@ -9656,12 +9645,12 @@
       <c r="B48" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="17" t="s">
         <v>78</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="19"/>
+      <c r="F48" s="18"/>
       <c r="G48" s="4"/>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -9688,7 +9677,7 @@
       <c r="B49" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="17" t="s">
         <v>80</v>
       </c>
       <c r="D49" s="4"/>
@@ -9720,8 +9709,8 @@
       <c r="B50" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="18"/>
-      <c r="D50" s="19" t="s">
+      <c r="C50" s="17"/>
+      <c r="D50" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E50" s="4"/>
@@ -9752,7 +9741,7 @@
       <c r="B51" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C51" s="14" t="s">
+      <c r="C51" s="13" t="s">
         <v>87</v>
       </c>
       <c r="D51" s="4"/>
@@ -9784,7 +9773,7 @@
       <c r="B52" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C52" s="20">
+      <c r="C52" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D52" s="4"/>
@@ -9816,7 +9805,7 @@
       <c r="B53" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C53" s="13" t="s">
+      <c r="C53" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D53" s="4"/>
@@ -9848,7 +9837,7 @@
       <c r="B54" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C54" s="13" t="s">
+      <c r="C54" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D54" s="4"/>
@@ -9880,7 +9869,7 @@
       <c r="B55" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D55" s="4"/>
@@ -9914,7 +9903,7 @@
       <c r="D56" s="4"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="19" t="s">
+      <c r="A57" s="18" t="s">
         <v>88</v>
       </c>
       <c r="B57" s="4"/>
@@ -9926,7 +9915,7 @@
       <c r="B58" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C58" s="13" t="s">
+      <c r="C58" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D58" s="4"/>
@@ -9936,11 +9925,11 @@
       <c r="B59" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="20" t="s">
         <v>65</v>
       </c>
       <c r="D59" s="4"/>
-      <c r="F59" s="8" t="s">
+      <c r="F59" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -9949,7 +9938,7 @@
       <c r="B60" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>89</v>
       </c>
       <c r="D60" s="4"/>
@@ -9960,7 +9949,7 @@
         <v>68</v>
       </c>
       <c r="C61" s="4"/>
-      <c r="D61" s="19" t="s">
+      <c r="D61" s="18" t="s">
         <v>90</v>
       </c>
     </row>
@@ -9969,7 +9958,7 @@
       <c r="B62" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C62" s="14" t="s">
+      <c r="C62" s="13" t="s">
         <v>91</v>
       </c>
       <c r="D62" s="4"/>
@@ -9979,7 +9968,7 @@
       <c r="B63" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C63" s="20">
+      <c r="C63" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D63" s="4"/>
@@ -9989,7 +9978,7 @@
       <c r="B64" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C64" s="13" t="s">
+      <c r="C64" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D64" s="4"/>
@@ -9999,7 +9988,7 @@
       <c r="B65" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C65" s="13" t="s">
+      <c r="C65" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D65" s="4"/>
@@ -10009,7 +9998,7 @@
       <c r="B66" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="17" t="s">
         <v>93</v>
       </c>
       <c r="D66" s="4"/>
@@ -10019,7 +10008,7 @@
       <c r="B67" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D67" s="4"/>
@@ -10027,17 +10016,17 @@
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
-      <c r="C68" s="18"/>
+      <c r="C68" s="17"/>
       <c r="D68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
-      <c r="C69" s="18"/>
+      <c r="C69" s="17"/>
       <c r="D69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="19" t="s">
+      <c r="A70" s="18" t="s">
         <v>94</v>
       </c>
       <c r="B70" s="4"/>
@@ -10049,11 +10038,11 @@
       <c r="B71" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C71" s="13" t="s">
+      <c r="C71" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D71" s="4"/>
-      <c r="F71" s="8" t="s">
+      <c r="F71" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10062,7 +10051,7 @@
       <c r="B72" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="21" t="s">
+      <c r="C72" s="20" t="s">
         <v>65</v>
       </c>
       <c r="D72" s="4"/>
@@ -10072,7 +10061,7 @@
       <c r="B73" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="22">
+      <c r="C73" s="21">
         <v>1.0</v>
       </c>
       <c r="D73" s="4"/>
@@ -10083,7 +10072,7 @@
         <v>68</v>
       </c>
       <c r="C74" s="4"/>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="18" t="s">
         <v>95</v>
       </c>
     </row>
@@ -10092,7 +10081,7 @@
       <c r="B75" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="22" t="s">
         <v>96</v>
       </c>
       <c r="D75" s="4"/>
@@ -10102,7 +10091,7 @@
       <c r="B76" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C76" s="20">
+      <c r="C76" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D76" s="4"/>
@@ -10112,7 +10101,7 @@
       <c r="B77" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D77" s="4"/>
@@ -10122,7 +10111,7 @@
       <c r="B78" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D78" s="4"/>
@@ -10132,7 +10121,7 @@
       <c r="B79" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="17" t="s">
         <v>93</v>
       </c>
       <c r="D79" s="4"/>
@@ -10142,7 +10131,7 @@
       <c r="B80" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D80" s="4"/>
@@ -10150,10 +10139,10 @@
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="17"/>
+      <c r="C81" s="16"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="19" t="s">
+      <c r="A82" s="18" t="s">
         <v>97</v>
       </c>
       <c r="B82" s="4"/>
@@ -10165,11 +10154,11 @@
       <c r="B83" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C83" s="13" t="s">
+      <c r="C83" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D83" s="4"/>
-      <c r="F83" s="8" t="s">
+      <c r="F83" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10178,7 +10167,7 @@
       <c r="B84" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="20" t="s">
         <v>65</v>
       </c>
       <c r="D84" s="4"/>
@@ -10188,7 +10177,7 @@
       <c r="B85" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="17" t="s">
         <v>89</v>
       </c>
       <c r="D85" s="4"/>
@@ -10199,7 +10188,7 @@
         <v>68</v>
       </c>
       <c r="C86" s="4"/>
-      <c r="D86" s="19" t="s">
+      <c r="D86" s="18" t="s">
         <v>90</v>
       </c>
     </row>
@@ -10208,7 +10197,7 @@
       <c r="B87" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>98</v>
       </c>
       <c r="D87" s="4"/>
@@ -10223,7 +10212,7 @@
       <c r="B88" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C88" s="20">
+      <c r="C88" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D88" s="4"/>
@@ -10238,18 +10227,18 @@
       <c r="B89" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C89" s="13" t="s">
+      <c r="C89" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D89" s="4"/>
-      <c r="F89" s="21"/>
+      <c r="F89" s="20"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C90" s="13" t="s">
+      <c r="C90" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D90" s="4"/>
@@ -10259,7 +10248,7 @@
       <c r="B91" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="17" t="s">
         <v>93</v>
       </c>
       <c r="D91" s="4"/>
@@ -10269,7 +10258,7 @@
       <c r="B92" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C92" s="18" t="s">
+      <c r="C92" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D92" s="4"/>
@@ -10277,17 +10266,17 @@
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
-      <c r="C93" s="18"/>
+      <c r="C93" s="17"/>
       <c r="D93" s="4"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
-      <c r="C94" s="18"/>
+      <c r="C94" s="17"/>
       <c r="D94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="19" t="s">
+      <c r="A95" s="18" t="s">
         <v>99</v>
       </c>
       <c r="B95" s="4"/>
@@ -10299,7 +10288,7 @@
       <c r="B96" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C96" s="13" t="s">
+      <c r="C96" s="12" t="s">
         <v>63</v>
       </c>
       <c r="D96" s="4"/>
@@ -10310,7 +10299,7 @@
       <c r="B97" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="C97" s="20" t="s">
         <v>65</v>
       </c>
       <c r="D97" s="4"/>
@@ -10321,7 +10310,7 @@
       <c r="B98" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C98" s="22">
+      <c r="C98" s="21">
         <v>1.0</v>
       </c>
       <c r="D98" s="4"/>
@@ -10333,7 +10322,7 @@
         <v>68</v>
       </c>
       <c r="C99" s="4"/>
-      <c r="D99" s="19" t="s">
+      <c r="D99" s="18" t="s">
         <v>95</v>
       </c>
     </row>
@@ -10342,7 +10331,7 @@
       <c r="B100" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="22" t="s">
         <v>100</v>
       </c>
       <c r="D100" s="4"/>
@@ -10352,7 +10341,7 @@
       <c r="B101" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C101" s="20">
+      <c r="C101" s="19">
         <v>-1.0E20</v>
       </c>
       <c r="D101" s="4"/>
@@ -10362,7 +10351,7 @@
       <c r="B102" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C102" s="13" t="s">
+      <c r="C102" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D102" s="4"/>
@@ -10372,7 +10361,7 @@
       <c r="B103" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C103" s="13" t="s">
+      <c r="C103" s="12" t="s">
         <v>73</v>
       </c>
       <c r="D103" s="4"/>
@@ -10382,7 +10371,7 @@
       <c r="B104" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C104" s="18" t="s">
+      <c r="C104" s="17" t="s">
         <v>93</v>
       </c>
       <c r="D104" s="4"/>
@@ -10392,7 +10381,7 @@
       <c r="B105" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C105" s="18" t="s">
+      <c r="C105" s="17" t="s">
         <v>76</v>
       </c>
       <c r="D105" s="4"/>
@@ -10400,8 +10389,8 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
-      <c r="B106" s="17"/>
-      <c r="C106" s="24"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="23"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
     </row>
@@ -10426,10 +10415,10 @@
       <c r="B109" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C109" s="21" t="s">
+      <c r="C109" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F109" s="8" t="s">
+      <c r="F109" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10438,7 +10427,7 @@
       <c r="B110" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C110" s="25">
+      <c r="C110" s="24">
         <v>1.0</v>
       </c>
     </row>
@@ -10447,8 +10436,8 @@
       <c r="B111" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C111" s="18"/>
-      <c r="D111" s="8" t="s">
+      <c r="C111" s="17"/>
+      <c r="D111" s="7" t="s">
         <v>102</v>
       </c>
     </row>
@@ -10457,7 +10446,7 @@
       <c r="B112" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C112" s="8" t="s">
+      <c r="C112" s="7" t="s">
         <v>103</v>
       </c>
     </row>
@@ -10466,7 +10455,7 @@
       <c r="B113" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C113" s="26">
+      <c r="C113" s="25">
         <v>-1.0E20</v>
       </c>
     </row>
@@ -10475,7 +10464,7 @@
       <c r="B114" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -10484,7 +10473,7 @@
       <c r="B115" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C115" s="13" t="s">
+      <c r="C115" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -10493,7 +10482,7 @@
       <c r="B116" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C116" s="18" t="s">
+      <c r="C116" s="17" t="s">
         <v>93</v>
       </c>
     </row>
@@ -10502,7 +10491,7 @@
       <c r="B117" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C117" s="18" t="s">
+      <c r="C117" s="17" t="s">
         <v>76</v>
       </c>
     </row>
@@ -10516,14 +10505,14 @@
         <v>104</v>
       </c>
       <c r="B119" s="4"/>
-      <c r="C119" s="17"/>
+      <c r="C119" s="16"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C120" s="27" t="s">
+      <c r="C120" s="26" t="s">
         <v>105</v>
       </c>
     </row>
@@ -10532,10 +10521,10 @@
       <c r="B121" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C121" s="21" t="s">
+      <c r="C121" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F121" s="8" t="s">
+      <c r="F121" s="7" t="s">
         <v>66</v>
       </c>
     </row>
@@ -10544,7 +10533,7 @@
       <c r="B122" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C122" s="25">
+      <c r="C122" s="24">
         <v>1.0</v>
       </c>
     </row>
@@ -10553,14 +10542,14 @@
       <c r="B123" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C123" s="25"/>
+      <c r="C123" s="24"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C124" s="27" t="s">
+      <c r="C124" s="26" t="s">
         <v>106</v>
       </c>
     </row>
@@ -10569,7 +10558,7 @@
       <c r="B125" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="13" t="s">
         <v>108</v>
       </c>
       <c r="D125" s="4"/>
@@ -10578,10 +10567,10 @@
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C126" s="24" t="s">
+      <c r="C126" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D126" s="4"/>
@@ -10592,21 +10581,21 @@
       <c r="A127" s="6"/>
       <c r="B127" s="6"/>
       <c r="C127" s="6"/>
-      <c r="F127" s="21"/>
+      <c r="F127" s="20"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="4" t="s">
         <v>111</v>
       </c>
       <c r="B128" s="4"/>
-      <c r="C128" s="17"/>
+      <c r="C128" s="16"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C129" s="27" t="s">
+      <c r="C129" s="26" t="s">
         <v>105</v>
       </c>
     </row>
@@ -10615,7 +10604,7 @@
       <c r="B130" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C130" s="21" t="s">
+      <c r="C130" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -10624,7 +10613,7 @@
       <c r="B131" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C131" s="25">
+      <c r="C131" s="24">
         <v>1.0</v>
       </c>
     </row>
@@ -10633,14 +10622,14 @@
       <c r="B132" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C132" s="25"/>
+      <c r="C132" s="24"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C133" s="27" t="s">
+      <c r="C133" s="26" t="s">
         <v>112</v>
       </c>
     </row>
@@ -10649,7 +10638,7 @@
       <c r="B134" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C134" s="14" t="s">
+      <c r="C134" s="13" t="s">
         <v>108</v>
       </c>
       <c r="D134" s="4"/>
@@ -10657,10 +10646,10 @@
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
-      <c r="B135" s="17" t="s">
+      <c r="B135" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C135" s="24" t="s">
+      <c r="C135" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D135" s="4"/>
@@ -10668,8 +10657,8 @@
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
-      <c r="B136" s="17"/>
-      <c r="C136" s="24"/>
+      <c r="B136" s="16"/>
+      <c r="C136" s="23"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
     </row>
@@ -10678,14 +10667,14 @@
         <v>113</v>
       </c>
       <c r="B137" s="4"/>
-      <c r="C137" s="17"/>
+      <c r="C137" s="16"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C138" s="27" t="s">
+      <c r="C138" s="26" t="s">
         <v>105</v>
       </c>
     </row>
@@ -10694,7 +10683,7 @@
       <c r="B139" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C139" s="21" t="s">
+      <c r="C139" s="20" t="s">
         <v>65</v>
       </c>
     </row>
@@ -10703,7 +10692,7 @@
       <c r="B140" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C140" s="25">
+      <c r="C140" s="24">
         <v>1.0</v>
       </c>
     </row>
@@ -10712,14 +10701,14 @@
       <c r="B141" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C141" s="25"/>
+      <c r="C141" s="24"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C142" s="28" t="s">
+      <c r="C142" s="26" t="s">
         <v>114</v>
       </c>
     </row>
@@ -10728,7 +10717,7 @@
       <c r="B143" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C143" s="14" t="s">
+      <c r="C143" s="13" t="s">
         <v>108</v>
       </c>
       <c r="D143" s="4"/>
@@ -10736,10 +10725,10 @@
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
-      <c r="B144" s="17" t="s">
+      <c r="B144" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C144" s="24" t="s">
+      <c r="C144" s="23" t="s">
         <v>110</v>
       </c>
       <c r="D144" s="4"/>
